--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-FRM-26_kalibrasyonu_uygunsuz__suresi_gecmis_cihazla_olculen_ur.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-FRM-26_kalibrasyonu_uygunsuz__suresi_gecmis_cihazla_olculen_ur.xlsx
@@ -992,7 +992,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-26&amp;C&amp;"Arial,Regular"&amp;11Kalibrasyonu Uygunsuz / Süresi Geçmiş Cihazla Ölçülen Ürün Etki Analizi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc3d2b157c7b47b3"/>
   <x:tableParts count="1">
@@ -1389,7 +1390,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-26&amp;C&amp;"Arial,Regular"&amp;11Kalibrasyonu Uygunsuz / Süresi Geçmiş Cihazla Ölçülen Ürün Etki Analizi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb60a5341734f8d"/>
   <x:tableParts count="1">
@@ -1720,7 +1722,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-26&amp;C&amp;"Arial,Regular"&amp;11Kalibrasyonu Uygunsuz / Süresi Geçmiş Cihazla Ölçülen Ürün Etki Analizi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e123c7e3cd441d6"/>
   <x:tableParts count="1">
@@ -2000,7 +2003,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-26&amp;C&amp;"Arial,Regular"&amp;11Kalibrasyonu Uygunsuz / Süresi Geçmiş Cihazla Ölçülen Ürün Etki Analizi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe7a85686bb4a1b"/>
   <x:tableParts count="1">
